--- a/CardArchive/Tools/DataExport/CardData.xlsx
+++ b/CardArchive/Tools/DataExport/CardData.xlsx
@@ -8,6 +8,44 @@
     <sheet name="CardData" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font/>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -406,37 +444,37 @@
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Type</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">설명</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">비고</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndField</t>
         </is>
@@ -1541,14 +1579,22 @@
       </c>
       <c r="P7"/>
       <c r="Q7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7"/>
-      <c r="T7"/>
-      <c r="U7"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Akashi_Junko/Akashi_Junko_Card.png</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Akashi_Junko/Akashi_Junko_Board.png</t>
+        </is>
+      </c>
       <c r="V7"/>
       <c r="W7"/>
       <c r="X7"/>
@@ -2455,41 +2501,53 @@
       <c r="C21"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flower</t>
+          <t xml:space="preserve">Field_Repair_Drone</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">푸른 장미</t>
+          <t xml:space="preserve">야전 정비 드론</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
-        </is>
-      </c>
-      <c r="L21"/>
+          <t xml:space="preserve">BACK</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP_heal_ally_select</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">긴급 수리</t>
+        </is>
+      </c>
       <c r="P21"/>
       <c r="Q21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -2513,21 +2571,21 @@
       <c r="C22"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forced_Relocation</t>
+          <t xml:space="preserve">Flower</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">강제 이동</t>
+          <t xml:space="preserve">푸른 장미</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2538,28 +2596,16 @@
       <c r="J22"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L22"/>
       <c r="M22"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spell_move_enemy_neighbor</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">적 유닛 하나를 지정해 주위 한 칸으로 이동시킵니다.</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">적 유닛 하나를 지정해 주위 한 칸으로 이동시킵니다.</t>
-        </is>
-      </c>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
       <c r="Q22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -2583,12 +2629,12 @@
       <c r="C23"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederica_Semla</t>
+          <t xml:space="preserve">Forced_Relocation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">프레데리카 셈라</t>
+          <t xml:space="preserve">강제 이동</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2597,7 +2643,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2615,17 +2661,21 @@
       <c r="M23"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_add_ally_hp5_restore</t>
+          <t xml:space="preserve">spell_move_enemy_neighbor</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">지정한 아군의 최대 체력을 5 증가시키고, 최대로 회복합니다.</t>
-        </is>
-      </c>
-      <c r="P23"/>
+          <t xml:space="preserve">적 유닛 하나를 지정해 주위 한 칸으로 이동시킵니다.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적 유닛 하나를 지정해 주위 한 칸으로 이동시킵니다.</t>
+        </is>
+      </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -2649,21 +2699,21 @@
       <c r="C24"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gourmet_Research_Society</t>
+          <t xml:space="preserve">Frederica_Semla</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">미식연구회</t>
+          <t xml:space="preserve">프레데리카 셈라</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2671,11 +2721,7 @@
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gourmet_Research_Society</t>
-        </is>
-      </c>
+      <c r="J24"/>
       <c r="K24" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE</t>
@@ -2685,12 +2731,12 @@
       <c r="M24"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHO_sabotage_not_full;OG_set_club_ui</t>
+          <t xml:space="preserve">spell_add_ally_hp5_restore</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">미식연구부 학생이 회복을 하고, 체력이 가득찬 상태가 아니라면 필드의 모든 유닛에게 미식연구부 학생 수만큼 피해를 줍니다.</t>
+          <t xml:space="preserve">지정한 아군의 최대 체력을 5 증가시키고, 최대로 회복합니다.</t>
         </is>
       </c>
       <c r="P24"/>
@@ -2719,53 +2765,53 @@
       <c r="C25"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hakari_Atsuko</t>
+          <t xml:space="preserve">Gourmet_Research_Society</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">하카리 아츠코</t>
+          <t xml:space="preserve">미식연구회</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Club</t>
         </is>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arius_Squad</t>
+          <t xml:space="preserve">Gourmet_Research_Society</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L25"/>
       <c r="M25"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_evasion</t>
+          <t xml:space="preserve">OHO_sabotage_not_full;OG_set_club_ui</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피</t>
+          <t xml:space="preserve">미식연구부 학생이 회복을 하고, 체력이 가득찬 상태가 아니라면 필드의 모든 유닛에게 미식연구부 학생 수만큼 피해를 줍니다.</t>
         </is>
       </c>
       <c r="P25"/>
       <c r="Q25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -2773,14 +2819,10 @@
       <c r="S25"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Hakari_Atsuko/Hakari_Atsuko_Card.png</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Hakari_Atsuko/Hakari_Atsuko_Board.png</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Gehenna/Gourmet_Research_Society/GourmetResearchClub.png</t>
+        </is>
+      </c>
+      <c r="U25"/>
       <c r="V25"/>
       <c r="W25"/>
       <c r="X25"/>
@@ -2797,56 +2839,68 @@
       <c r="C26"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Halo_Destroying_Bomb</t>
+          <t xml:space="preserve">Hakari_Atsuko</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">헤일로를 파괴하는 폭탄</t>
+          <t xml:space="preserve">하카리 아츠코</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26"/>
+        <v>4</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arius_Squad</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L26"/>
       <c r="M26"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_destroy_halo</t>
+          <t xml:space="preserve">OG_evasion</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">적 학생 한 명의 헤일로를 파괴합니다</t>
+          <t xml:space="preserve">회피</t>
         </is>
       </c>
       <c r="P26"/>
       <c r="Q26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26"/>
-      <c r="T26"/>
-      <c r="U26"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Hakari_Atsuko/Hakari_Atsuko_Card.png</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Hakari_Atsuko/Hakari_Atsuko_Board.png</t>
+        </is>
+      </c>
       <c r="V26"/>
       <c r="W26"/>
       <c r="X26"/>
@@ -2863,68 +2917,56 @@
       <c r="C27"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanekawa_Hasumi</t>
+          <t xml:space="preserve">Halo_Destroying_Bomb</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">하네카와 하스미</t>
+          <t xml:space="preserve">헤일로를 파괴하는 폭탄</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G27">
         <v>4</v>
       </c>
       <c r="H27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>2</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Justice_Task_Force</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J27"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L27"/>
       <c r="M27"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_add_ATK_HP1_JTFM</t>
+          <t xml:space="preserve">OP_destroy_halo</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 자신의 '정의실현부 부원'에게 1/1을 부여합니다.</t>
+          <t xml:space="preserve">적 학생 한 명의 헤일로를 파괴합니다</t>
         </is>
       </c>
       <c r="P27"/>
       <c r="Q27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27"/>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Hanekawa_Hasumi/Hanekawa_Hasumi_Card.png</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Hanekawa_Hasumi/Hanekawa_Hasumi_Board.png</t>
-        </is>
-      </c>
+      <c r="T27"/>
+      <c r="U27"/>
       <c r="V27"/>
       <c r="W27"/>
       <c r="X27"/>
@@ -2941,49 +2983,53 @@
       <c r="C28"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hot_Spring</t>
+          <t xml:space="preserve">Hanekawa_Hasumi</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">온천</t>
+          <t xml:space="preserve">하네카와 하스미</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>2</v>
       </c>
-      <c r="J28"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Justice_Task_Force</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L28"/>
       <c r="M28"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">play_heal2</t>
+          <t xml:space="preserve">OG_add_ATK_HP1_JTFM</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 지정한 아군 유닛의 체력을 2 회복합니다.</t>
+          <t xml:space="preserve">등교 : 자신의 '정의실현부 부원'에게 1/1을 부여합니다.</t>
         </is>
       </c>
       <c r="P28"/>
       <c r="Q28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -2991,12 +3037,12 @@
       <c r="S28"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/Hot_Spring/Hot_Spring_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Hanekawa_Hasumi/Hanekawa_Hasumi_Card.png</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/Hot_Spring/Hot_Spring_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Hanekawa_Hasumi/Hanekawa_Hasumi_Board.png</t>
         </is>
       </c>
       <c r="V28"/>
@@ -3015,72 +3061,52 @@
       <c r="C29"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hot_Springs_Department</t>
+          <t xml:space="preserve">Heavy_Sentry_Robot</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">온천개발부</t>
+          <t xml:space="preserve">중장갑 경비 로봇</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hot_Springs_Department</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J29"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
-        </is>
-      </c>
-      <c r="L29"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M29"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OAAO_HSD_destroy_place;OG_set_club_ui</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">온천개발부원이 장소를 공격하면, 파괴 후 온천을 소환합니다..</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">게헨나 학원의 온천개발부</t>
-        </is>
-      </c>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
       <c r="Q29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29"/>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Gehenna/Hot_Spring_Department/Hot_Spring_Department_Card.png</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Gehenna/Hot_Sprint_Deparment_Icon.png</t>
-        </is>
-      </c>
+      <c r="T29"/>
+      <c r="U29"/>
       <c r="V29"/>
       <c r="W29"/>
       <c r="X29"/>
@@ -3097,48 +3123,44 @@
       <c r="C30"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ibaragi_Yoshimi</t>
+          <t xml:space="preserve">Hot_Spring</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">이바라기 요시미</t>
+          <t xml:space="preserve">온천</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>2</v>
       </c>
-      <c r="H30">
-        <v>2</v>
-      </c>
-      <c r="I30">
-        <v>3</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">After_School_Sweets_Club</t>
-        </is>
-      </c>
+      <c r="J30"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L30"/>
       <c r="M30"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_create_self_cafe</t>
+          <t xml:space="preserve">play_heal2</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : '카페'를 패로 가져옵니다.</t>
+          <t xml:space="preserve">등교 : 지정한 아군 유닛의 체력을 2 회복합니다.</t>
         </is>
       </c>
       <c r="P30"/>
@@ -3149,8 +3171,16 @@
         <v>100</v>
       </c>
       <c r="S30"/>
-      <c r="T30"/>
-      <c r="U30"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/Hot_Spring/Hot_Spring_Card.png</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/Hot_Spring/Hot_Spring_Board.png</t>
+        </is>
+      </c>
       <c r="V30"/>
       <c r="W30"/>
       <c r="X30"/>
@@ -3167,53 +3197,57 @@
       <c r="C31"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imashino_Misaki</t>
+          <t xml:space="preserve">Hot_Springs_Department</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">이마시노 미사키</t>
+          <t xml:space="preserve">온천개발부</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Club</t>
         </is>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arius_Squad</t>
+          <t xml:space="preserve">Hot_Springs_Department</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L31"/>
       <c r="M31"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">OAAO_SI_slot_mine</t>
+          <t xml:space="preserve">OAAO_HSD_destroy_place;OG_set_club_ui</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신의 필드에 위치하면, 공격 후 체력 1을 잃습니다.</t>
-        </is>
-      </c>
-      <c r="P31"/>
+          <t xml:space="preserve">온천개발부원이 장소를 공격하면, 파괴 후 온천을 소환합니다..</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게헨나 학원의 온천개발부</t>
+        </is>
+      </c>
       <c r="Q31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -3221,12 +3255,12 @@
       <c r="S31"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Imashino_Misaki/Imashino_Misaki_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Gehenna/Hot_Spring_Department/Hot_Spring_Department_Card.png</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Imashino_Misaki/Imashino_Misaki_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Gehenna/Hot_Sprint_Deparment_Icon.png</t>
         </is>
       </c>
       <c r="V31"/>
@@ -3245,12 +3279,12 @@
       <c r="C32"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joumae_Saori</t>
+          <t xml:space="preserve">Ibaragi_Yoshimi</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">조마에 사오리</t>
+          <t xml:space="preserve">이바라기 요시미</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3259,17 +3293,17 @@
         </is>
       </c>
       <c r="G32">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arius_Squad</t>
+          <t xml:space="preserve">After_School_Sweets_Club</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3281,32 +3315,24 @@
       <c r="M32"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_damage_target_7</t>
+          <t xml:space="preserve">OP_create_self_cafe</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 지정한 적에게 피해를 7 줍니다.</t>
+          <t xml:space="preserve">등교 : '카페'를 패로 가져옵니다.</t>
         </is>
       </c>
       <c r="P32"/>
       <c r="Q32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Joumae_Saori/Joumae_Saori_Card.png</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Joumae_Saori/Joumae_Saori_Board.png</t>
-        </is>
-      </c>
+      <c r="T32"/>
+      <c r="U32"/>
       <c r="V32"/>
       <c r="W32"/>
       <c r="X32"/>
@@ -3323,53 +3349,53 @@
       <c r="C33"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justice_Task_Force</t>
+          <t xml:space="preserve">Imashino_Misaki</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">정의실현부</t>
+          <t xml:space="preserve">이마시노 미사키</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justice_Task_Force</t>
+          <t xml:space="preserve">Arius_Squad</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L33"/>
       <c r="M33"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODO_summon_JTFM1;OG_set_club_ui</t>
+          <t xml:space="preserve">OAAO_SI_slot_mine</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신의 유닛이 죽으면, 필드에 존재하는 아군 정의실현부 부원 수만큼 '정의실현부 부원'을 무작위 타일에 소환합니다.</t>
+          <t xml:space="preserve">자신의 필드에 위치하면, 공격 후 체력 1을 잃습니다.</t>
         </is>
       </c>
       <c r="P33"/>
       <c r="Q33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -3377,10 +3403,14 @@
       <c r="S33"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Trinity/Justice_Task_Force_Card.png</t>
-        </is>
-      </c>
-      <c r="U33"/>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Imashino_Misaki/Imashino_Misaki_Card.png</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Imashino_Misaki/Imashino_Misaki_Board.png</t>
+        </is>
+      </c>
       <c r="V33"/>
       <c r="W33"/>
       <c r="X33"/>
@@ -3397,29 +3427,33 @@
       <c r="C34"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justice_Task_Force_Memeber</t>
+          <t xml:space="preserve">Joumae_Saori</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">정의실현부 부원</t>
+          <t xml:space="preserve">조마에 사오리</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>1</v>
-      </c>
-      <c r="J34"/>
+        <v>6</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arius_Squad</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">MIDDLE</t>
@@ -3427,11 +3461,19 @@
       </c>
       <c r="L34"/>
       <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP_damage_target_7</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등교 : 지정한 적에게 피해를 7 줍니다.</t>
+        </is>
+      </c>
       <c r="P34"/>
       <c r="Q34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -3439,12 +3481,12 @@
       <c r="S34"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Justice_Task_Force_Member/Justice_Task_Force_Member_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Joumae_Saori/Joumae_Saori_Card.png</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Justice_Task_Force_Member/Justice_Task_Force_Member_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Joumae_Saori/Joumae_Saori_Board.png</t>
         </is>
       </c>
       <c r="V34"/>
@@ -3463,51 +3505,63 @@
       <c r="C35"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaiser_PMC_Drone</t>
+          <t xml:space="preserve">Justice_Task_Force</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">카이저 PMC 드론</t>
+          <t xml:space="preserve">정의실현부</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Club</t>
         </is>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="J35"/>
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Justice_Task_Force</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+          <t xml:space="preserve">NONE</t>
+        </is>
+      </c>
+      <c r="L35"/>
       <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ODO_summon_JTFM1;OG_set_club_ui</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자신의 유닛이 죽으면, 필드에 존재하는 아군 정의실현부 부원 수만큼 '정의실현부 부원'을 무작위 타일에 소환합니다.</t>
+        </is>
+      </c>
       <c r="P35"/>
       <c r="Q35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35"/>
-      <c r="T35"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Trinity/Justice_Task_Force_Card.png</t>
+        </is>
+      </c>
       <c r="U35"/>
       <c r="V35"/>
       <c r="W35"/>
@@ -3525,46 +3579,38 @@
       <c r="C36"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaiser_Supply</t>
+          <t xml:space="preserve">Justice_Task_Force_Memeber</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">카이저 지원군</t>
+          <t xml:space="preserve">정의실현부 부원</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L36"/>
       <c r="M36"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OP_summon_Kaiser_PMC_Drone_Unit</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'카이저 PMC 드론' (2/1) 3개를 소환합니다.</t>
-        </is>
-      </c>
+      <c r="N36"/>
+      <c r="O36"/>
       <c r="P36"/>
       <c r="Q36">
         <v>0</v>
@@ -3573,8 +3619,16 @@
         <v>100</v>
       </c>
       <c r="S36"/>
-      <c r="T36"/>
-      <c r="U36"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Justice_Task_Force_Member/Justice_Task_Force_Member_Card.png</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Justice_Task_Force_Member/Justice_Task_Force_Member_Board.png</t>
+        </is>
+      </c>
       <c r="V36"/>
       <c r="W36"/>
       <c r="X36"/>
@@ -3591,68 +3645,52 @@
       <c r="C37"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenzaki_Tsurugi</t>
+          <t xml:space="preserve">Kaiser_PMC_Drone</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">켄자키 츠루기</t>
+          <t xml:space="preserve">카이저 PMC 드론</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37">
-        <v>6</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Justice_Task_Force</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J37"/>
       <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L37"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M37"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OU_haste;OG_mass_shooting;OK_regeneration_self</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">난사, 적을 처치하면 체력을 회복합니다.</t>
-        </is>
-      </c>
+      <c r="N37"/>
+      <c r="O37"/>
       <c r="P37"/>
       <c r="Q37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37"/>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Kenzaki_Tsurugi/Kenzaki_Tsurugi_Card.png</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Kenzaki_Tsurugi/Kenzaki_Tsurugi_Board.png</t>
-        </is>
-      </c>
+      <c r="T37"/>
+      <c r="U37"/>
       <c r="V37"/>
       <c r="W37"/>
       <c r="X37"/>
@@ -3669,78 +3707,62 @@
       <c r="C38"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kinugawa_Kasumi</t>
+          <t xml:space="preserve">Kaiser_Supply</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">키누가와 카스미</t>
+          <t xml:space="preserve">카이저 지원군</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hot_Springs_Department</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J38"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L38"/>
       <c r="M38"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_kill_except1</t>
+          <t xml:space="preserve">OP_summon_Kaiser_PMC_Drone_Unit</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 무작위 유닛 하나를 제외하고 모두 파괴합니다.</t>
+          <t xml:space="preserve">'카이저 PMC 드론' (2/1) 3개를 소환합니다.</t>
         </is>
       </c>
       <c r="P38"/>
       <c r="Q38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38">
         <v>100</v>
       </c>
       <c r="S38"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Kinugawa_Kasumi/Kinugawa_Kasumi_Card.png</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Kinugawa_Kasumi/Kinugawa_Kasumi_Board.png</t>
-        </is>
-      </c>
+      <c r="T38"/>
+      <c r="U38"/>
       <c r="V38"/>
       <c r="W38"/>
       <c r="X38"/>
       <c r="Y38"/>
       <c r="Z38"/>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Gehenna/Hot_Spring_Department/Kasumi/Kasumi_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38"/>
@@ -3751,12 +3773,12 @@
       <c r="C39"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirifuji_Nagisa</t>
+          <t xml:space="preserve">Kenzaki_Tsurugi</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">키리후지 나기사</t>
+          <t xml:space="preserve">켄자키 츠루기</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3765,36 +3787,36 @@
         </is>
       </c>
       <c r="G39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tea_Party</t>
+          <t xml:space="preserve">Justice_Task_Force</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L39"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tea_party_host=2</t>
-        </is>
-      </c>
+      <c r="M39"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">EOT_Bombard_Store;SOT_Bombard_Fire</t>
-        </is>
-      </c>
-      <c r="O39"/>
+          <t xml:space="preserve">OU_haste;OG_mass_shooting;OK_regeneration_self</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">난사, 적을 처치하면 체력을 회복합니다.</t>
+        </is>
+      </c>
       <c r="P39"/>
       <c r="Q39">
         <v>1</v>
@@ -3803,8 +3825,16 @@
         <v>100</v>
       </c>
       <c r="S39"/>
-      <c r="T39"/>
-      <c r="U39"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Kenzaki_Tsurugi/Kenzaki_Tsurugi_Card.png</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Kenzaki_Tsurugi/Kenzaki_Tsurugi_Board.png</t>
+        </is>
+      </c>
       <c r="V39"/>
       <c r="W39"/>
       <c r="X39"/>
@@ -3821,12 +3851,12 @@
       <c r="C40"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kurimura_Airi</t>
+          <t xml:space="preserve">Kinugawa_Kasumi</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">쿠리무라 아이리</t>
+          <t xml:space="preserve">키누가와 카스미</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3835,52 +3865,64 @@
         </is>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">After_School_Sweets_Club</t>
+          <t xml:space="preserve">Hot_Springs_Department</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L40"/>
       <c r="M40"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">OAD_summon_ASSC</t>
+          <t xml:space="preserve">OP_kill_except1</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 카드가 공격 받으면 덱에서 무작위 방과후 디저트 부 학생을 하나 필드에 무작위 소환합니다.</t>
+          <t xml:space="preserve">등교 : 무작위 유닛 하나를 제외하고 모두 파괴합니다.</t>
         </is>
       </c>
       <c r="P40"/>
       <c r="Q40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40">
         <v>100</v>
       </c>
       <c r="S40"/>
-      <c r="T40"/>
-      <c r="U40"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Kinugawa_Kasumi/Kinugawa_Kasumi_Card.png</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Kinugawa_Kasumi/Kinugawa_Kasumi_Board.png</t>
+        </is>
+      </c>
       <c r="V40"/>
       <c r="W40"/>
       <c r="X40"/>
       <c r="Y40"/>
       <c r="Z40"/>
-      <c r="AA40"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Gehenna/Hot_Spring_Department/Kasumi/Kasumi_CommonSkill.mp3</t>
+        </is>
+      </c>
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40"/>
@@ -3891,12 +3933,12 @@
       <c r="C41"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kurodate_Haruna</t>
+          <t xml:space="preserve">Kirifuji_Nagisa</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">쿠로다테 하루나</t>
+          <t xml:space="preserve">키리후지 나기사</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3905,17 +3947,17 @@
         </is>
       </c>
       <c r="G41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gourmet_Research_Society</t>
+          <t xml:space="preserve">Tea_Party</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3924,16 +3966,20 @@
         </is>
       </c>
       <c r="L41"/>
-      <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미식연구부 동아리 효과 발동 시, 추가 피해 5를 입힌다.</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tea_party_host=2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOT_Bombard_Store;SOT_Bombard_Fire</t>
+        </is>
+      </c>
+      <c r="O41"/>
       <c r="P41"/>
       <c r="Q41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41">
         <v>100</v>
@@ -3957,12 +4003,12 @@
       <c r="C42"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kyouyama_Kazusa</t>
+          <t xml:space="preserve">Kurimura_Airi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">쿄야마 카즈사</t>
+          <t xml:space="preserve">쿠리무라 아이리</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3974,11 +4020,11 @@
         <v>4</v>
       </c>
       <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
         <v>4</v>
       </c>
-      <c r="I42">
-        <v>3</v>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t xml:space="preserve">After_School_Sweets_Club</t>
@@ -3986,19 +4032,19 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L42"/>
       <c r="M42"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ODO_damage_BD</t>
+          <t xml:space="preserve">OAD_summon_ASSC</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve">건물이 파괴되면 건물을 파괴한 유닛에게 카즈사 공격력 만큼의 데미지를 준다.</t>
+          <t xml:space="preserve">이 카드가 공격 받으면 덱에서 무작위 방과후 디저트 부 학생을 하나 필드에 무작위 소환합니다.</t>
         </is>
       </c>
       <c r="P42"/>
@@ -4027,56 +4073,68 @@
       <c r="C43"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Macaroon</t>
+          <t xml:space="preserve">Kurodate_Haruna</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">마카롱</t>
+          <t xml:space="preserve">쿠로다테 하루나</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43"/>
+        <v>4</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gourmet_Research_Society</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L43"/>
       <c r="M43"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_add_ally_attack1</t>
+          <t xml:space="preserve">OG_haruna_gourmet_mark</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">지정한 아군의 공격력이 1 증가합니다.</t>
+          <t xml:space="preserve">미식연구부 동아리 효과가 피해 대신 파괴로 바뀐다.</t>
         </is>
       </c>
       <c r="P43"/>
       <c r="Q43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43">
         <v>100</v>
       </c>
       <c r="S43"/>
-      <c r="T43"/>
-      <c r="U43"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Kurodate_Haruna/Kurodate_Haruna_Card.png</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Kurodate_Haruna/Kurodate_Haruna_Board.png</t>
+        </is>
+      </c>
       <c r="V43"/>
       <c r="W43"/>
       <c r="X43"/>
@@ -4093,53 +4151,53 @@
       <c r="C44"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maid_Cafe_Candy_Candy</t>
+          <t xml:space="preserve">Kyouyama_Kazusa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">메이드카페 캔디캔디</t>
+          <t xml:space="preserve">쿄야마 카즈사</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I44">
-        <v>4</v>
-      </c>
-      <c r="J44"/>
+        <v>3</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After_School_Sweets_Club</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L44"/>
       <c r="M44"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_add_atk_hp1_ally_neighbor1</t>
+          <t xml:space="preserve">ODO_damage_BD</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve">주위 한칸의 아군 유닛에게 1/1을 부여합니다</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주위 한칸의 아군 유닛에게 1/1을 부여합니다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">건물이 파괴되면 건물을 파괴한 유닛에게 카즈사 공격력 만큼의 데미지를 준다.</t>
+        </is>
+      </c>
+      <c r="P44"/>
       <c r="Q44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44">
         <v>100</v>
@@ -4163,21 +4221,21 @@
       <c r="C45"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make_Up_Work_Club</t>
+          <t xml:space="preserve">Macaroon</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">보충수업부</t>
+          <t xml:space="preserve">마카롱</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -4185,11 +4243,7 @@
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Make_Up_Work_Club</t>
-        </is>
-      </c>
+      <c r="J45"/>
       <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE</t>
@@ -4199,12 +4253,12 @@
       <c r="M45"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPO_add_attack1_MUWC;OG_set_club_ui</t>
+          <t xml:space="preserve">spell_add_ally_attack1</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신이 카드를 사용할 때마다, 자신의 보충수업부 학생들이 공격력을 1 얻습니다.</t>
+          <t xml:space="preserve">지정한 아군의 공격력이 1 증가합니다.</t>
         </is>
       </c>
       <c r="P45"/>
@@ -4215,16 +4269,8 @@
         <v>100</v>
       </c>
       <c r="S45"/>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Trinity/Make_Up_Work_Club_Card.png</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Trinity/Make_Up_Work_Club_Icon.png</t>
-        </is>
-      </c>
+      <c r="T45"/>
+      <c r="U45"/>
       <c r="V45"/>
       <c r="W45"/>
       <c r="X45"/>
@@ -4241,12 +4287,12 @@
       <c r="C46"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Makoto_Statue</t>
+          <t xml:space="preserve">Maid_Cafe_Candy_Candy</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">마코토 동상</t>
+          <t xml:space="preserve">메이드카페 캔디캔디</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4255,13 +4301,13 @@
         </is>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J46"/>
       <c r="K46" t="inlineStr">
@@ -4273,17 +4319,21 @@
       <c r="M46"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_attack_m3</t>
+          <t xml:space="preserve">OG_add_atk_hp1_ally_neighbor1</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve">주변 한 칸의 모든 유닛은 공격력이 3 감소합니다</t>
-        </is>
-      </c>
-      <c r="P46"/>
+          <t xml:space="preserve">주위 한칸의 아군 유닛에게 1/1을 부여합니다</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주위 한칸의 아군 유닛에게 1/1을 부여합니다</t>
+        </is>
+      </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <v>100</v>
@@ -4307,21 +4357,21 @@
       <c r="C47"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Masters_Assistance</t>
+          <t xml:space="preserve">Make_Up_Work_Club</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">마이스터의 도움</t>
+          <t xml:space="preserve">보충수업부</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">Club</t>
         </is>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -4329,7 +4379,11 @@
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Make_Up_Work_Club</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE</t>
@@ -4339,12 +4393,12 @@
       <c r="M47"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_draw_machine2</t>
+          <t xml:space="preserve">OPO_add_attack1_MUWC;OG_set_club_ui</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신의 덱에서 무작위 기계 2장을 패로 가져옵니다.</t>
+          <t xml:space="preserve">자신이 카드를 사용할 때마다, 자신의 보충수업부 학생들이 공격력을 1 얻습니다.</t>
         </is>
       </c>
       <c r="P47"/>
@@ -4357,10 +4411,14 @@
       <c r="S47"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Event/Maister_Assiatance/Masters_Assistance_Card.png</t>
-        </is>
-      </c>
-      <c r="U47"/>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Trinity/Make_Up_Work_Club_Card.png</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Trinity/Make_Up_Work_Club_Icon.png</t>
+        </is>
+      </c>
       <c r="V47"/>
       <c r="W47"/>
       <c r="X47"/>
@@ -4377,27 +4435,27 @@
       <c r="C48"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk</t>
+          <t xml:space="preserve">Makoto_Statue</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">우유</t>
+          <t xml:space="preserve">마코토 동상</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J48"/>
       <c r="K48" t="inlineStr">
@@ -4409,17 +4467,17 @@
       <c r="M48"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_remove_bad_status_heal2</t>
+          <t xml:space="preserve">OG_attack_m3</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상의 디버프를 제거하고, 체력을 2 회복합니다.</t>
+          <t xml:space="preserve">주변 한 칸의 모든 유닛은 공격력이 3 감소합니다</t>
         </is>
       </c>
       <c r="P48"/>
       <c r="Q48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <v>100</v>
@@ -4443,12 +4501,12 @@
       <c r="C49"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">MintChoco_Wave</t>
+          <t xml:space="preserve">Masters_Assistance</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">민트초코 웨이브</t>
+          <t xml:space="preserve">마이스터의 도움</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4475,12 +4533,12 @@
       <c r="M49"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">mintchoco_wave</t>
+          <t xml:space="preserve">OP_draw_machine2</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">민트 초코를 싫어하는 시민에게는 3의 피해를, 좋아하는 시민에게는 3을 치유합니다.</t>
+          <t xml:space="preserve">자신의 덱에서 무작위 기계 2장을 패로 가져옵니다.</t>
         </is>
       </c>
       <c r="P49"/>
@@ -4491,7 +4549,11 @@
         <v>100</v>
       </c>
       <c r="S49"/>
-      <c r="T49"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Event/Maister_Assiatance/Masters_Assistance_Card.png</t>
+        </is>
+      </c>
       <c r="U49"/>
       <c r="V49"/>
       <c r="W49"/>
@@ -4509,21 +4571,21 @@
       <c r="C50"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miracle_5000</t>
+          <t xml:space="preserve">Milk</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">미라클 5000</t>
+          <t xml:space="preserve">우유</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="G50">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -4541,12 +4603,12 @@
       <c r="M50"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_restore_player_full</t>
+          <t xml:space="preserve">spell_remove_bad_status_heal2</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve">아군 본체의 체력을 최대로 회복합니다</t>
+          <t xml:space="preserve">대상의 디버프를 제거하고, 체력을 2 회복합니다.</t>
         </is>
       </c>
       <c r="P50"/>
@@ -4575,53 +4637,49 @@
       <c r="C51"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misono_Mika</t>
+          <t xml:space="preserve">MintChoco_Wave</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">미소노 미카</t>
+          <t xml:space="preserve">민트초코 웨이브</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>2</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tea_Party</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J51"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L51"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tea_party_host=1</t>
-        </is>
-      </c>
+      <c r="M51"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_trample</t>
-        </is>
-      </c>
-      <c r="O51"/>
+          <t xml:space="preserve">mintchoco_wave</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민트 초코를 싫어하는 시민에게는 3의 피해를, 좋아하는 시민에게는 3을 치유합니다.</t>
+        </is>
+      </c>
       <c r="P51"/>
       <c r="Q51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51">
         <v>100</v>
@@ -4645,68 +4703,56 @@
       <c r="C52"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modded_Sweeper</t>
+          <t xml:space="preserve">Miracle_5000</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">개조 스위퍼</t>
+          <t xml:space="preserve">미라클 5000</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J52"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+          <t xml:space="preserve">NONE</t>
+        </is>
+      </c>
+      <c r="L52"/>
       <c r="M52"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">OD_summon_Sweeper</t>
+          <t xml:space="preserve">spell_restore_player_full</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">하교 : '스위퍼' (1/1)을 소환합니다.</t>
+          <t xml:space="preserve">아군 본체의 체력을 최대로 회복합니다</t>
         </is>
       </c>
       <c r="P52"/>
       <c r="Q52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52">
         <v>100</v>
       </c>
       <c r="S52"/>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Card.png</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Board.png</t>
-        </is>
-      </c>
+      <c r="T52"/>
+      <c r="U52"/>
       <c r="V52"/>
       <c r="W52"/>
       <c r="X52"/>
@@ -4723,21 +4769,21 @@
       <c r="C53"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modded_Sweeper_Tutorial</t>
+          <t xml:space="preserve">Misono_Mika</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">개조 스위퍼</t>
+          <t xml:space="preserve">미소노 미카</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H53">
         <v>2</v>
@@ -4745,46 +4791,38 @@
       <c r="I53">
         <v>2</v>
       </c>
-      <c r="J53"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tea_Party</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
-      <c r="M53"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L53"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tea_party_host=1</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">OD_summon_Sweeper_Tutorial</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하교 : '스위퍼' (1/1)을 소환합니다.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">OG_trample</t>
+        </is>
+      </c>
+      <c r="O53"/>
       <c r="P53"/>
       <c r="Q53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53">
         <v>100</v>
       </c>
       <c r="S53"/>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Card.png</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Board.png</t>
-        </is>
-      </c>
+      <c r="T53"/>
+      <c r="U53"/>
       <c r="V53"/>
       <c r="W53"/>
       <c r="X53"/>
@@ -4801,48 +4839,48 @@
       <c r="C54"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Morizuki_Suzumi</t>
+          <t xml:space="preserve">Mobile_Recon_Drone</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">모리즈키 스즈미</t>
+          <t xml:space="preserve">기동 정찰 드론</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
         <v>2</v>
       </c>
-      <c r="I54">
-        <v>3</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
-        </is>
-      </c>
+      <c r="J54"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
-        </is>
-      </c>
-      <c r="L54"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M54"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_all_enemy_range_paralysed</t>
+          <t xml:space="preserve">move_add_attack1</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 지정한 유닛에게 기절을 부여합니다.</t>
+          <t xml:space="preserve">기동 전술</t>
         </is>
       </c>
       <c r="P54"/>
@@ -4853,26 +4891,14 @@
         <v>100</v>
       </c>
       <c r="S54"/>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Suzumi/Suzumi_Card.png</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Suzumi/Suzumi_Board.png</t>
-        </is>
-      </c>
+      <c r="T54"/>
+      <c r="U54"/>
       <c r="V54"/>
       <c r="W54"/>
       <c r="X54"/>
       <c r="Y54"/>
       <c r="Z54"/>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Trinity/Trinity_Vigilante_Crew/Suzumi/Suzumi_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA54"/>
       <c r="AB54"/>
       <c r="AC54"/>
       <c r="AD54"/>
@@ -4883,48 +4909,48 @@
       <c r="C55"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nakamasa_Ichika</t>
+          <t xml:space="preserve">Modded_Sweeper</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">나카마사 이치카</t>
+          <t xml:space="preserve">개조 스위퍼</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55">
-        <v>4</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Justice_Task_Force</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J55"/>
       <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
-      <c r="L55"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M55"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_summon_JTFM_besides</t>
+          <t xml:space="preserve">OD_summon_Sweeper</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 자신의 양 옆에 '정의실현부 부원'을 소환합니다.</t>
+          <t xml:space="preserve">하교 : '스위퍼' (1/1)을 소환합니다.</t>
         </is>
       </c>
       <c r="P55"/>
@@ -4937,12 +4963,12 @@
       <c r="S55"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Nakamasa_Ichika/Nakamasa_Ichika_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Card.png</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Nakamasa_Ichika/Nakamasa_Ichika_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Board.png</t>
         </is>
       </c>
       <c r="V55"/>
@@ -4961,53 +4987,53 @@
       <c r="C56"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nekozuka_Hibiki</t>
+          <t xml:space="preserve">Modded_Sweeper_Tutorial</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">네코즈카 히비키</t>
+          <t xml:space="preserve">개조 스위퍼</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I56">
-        <v>1</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J56"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
-        </is>
-      </c>
-      <c r="L56"/>
+          <t xml:space="preserve">MIDDLE</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M56"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_damage1_X</t>
+          <t xml:space="preserve">OD_summon_Sweeper_Tutorial</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 지정한 범위의 타일에 피해를 1 줍니다.</t>
+          <t xml:space="preserve">하교 : '스위퍼' (1/1)을 소환합니다.</t>
         </is>
       </c>
       <c r="P56"/>
       <c r="Q56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56">
         <v>100</v>
@@ -5015,12 +5041,12 @@
       <c r="S56"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Card.png</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Modded_Sweeper/Modded_Sweeper_Board.png</t>
         </is>
       </c>
       <c r="V56"/>
@@ -5028,11 +5054,7 @@
       <c r="X56"/>
       <c r="Y56"/>
       <c r="Z56"/>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Hibiki/Hibiki_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA56"/>
       <c r="AB56"/>
       <c r="AC56"/>
       <c r="AD56"/>
@@ -5043,12 +5065,12 @@
       <c r="C57"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nekozuka_Hibiki_Tutorial</t>
+          <t xml:space="preserve">Morizuki_Suzumi</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">네코즈카 히비키</t>
+          <t xml:space="preserve">모리즈키 스즈미</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5057,39 +5079,39 @@
         </is>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H57">
+        <v>2</v>
+      </c>
+      <c r="I57">
         <v>3</v>
       </c>
-      <c r="I57">
-        <v>1</v>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engineering_Department</t>
+          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L57"/>
       <c r="M57"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_damage1_X;OG_taunt</t>
+          <t xml:space="preserve">OP_all_enemy_range_paralysed</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 지정한 범위의 타일에 피해를 1 줍니다.</t>
+          <t xml:space="preserve">등교 : 지정한 유닛에게 기절을 부여합니다.</t>
         </is>
       </c>
       <c r="P57"/>
       <c r="Q57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57">
         <v>100</v>
@@ -5097,12 +5119,12 @@
       <c r="S57"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Suzumi/Suzumi_Card.png</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Suzumi/Suzumi_Board.png</t>
         </is>
       </c>
       <c r="V57"/>
@@ -5112,7 +5134,7 @@
       <c r="Z57"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Hibiki/Hibiki_CommonSkill.mp3</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Trinity/Trinity_Vigilante_Crew/Suzumi/Suzumi_CommonSkill.mp3</t>
         </is>
       </c>
       <c r="AB57"/>
@@ -5125,29 +5147,33 @@
       <c r="C58"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">New_Club_Member</t>
+          <t xml:space="preserve">Nakamasa_Ichika</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">신입 동아리원</t>
+          <t xml:space="preserve">나카마사 이치카</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G58">
+        <v>6</v>
+      </c>
+      <c r="H58">
         <v>4</v>
       </c>
-      <c r="H58">
-        <v>2</v>
-      </c>
       <c r="I58">
-        <v>3</v>
-      </c>
-      <c r="J58"/>
+        <v>4</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Justice_Task_Force</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t xml:space="preserve">MIDDLE</t>
@@ -5157,12 +5183,12 @@
       <c r="M58"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice_club</t>
+          <t xml:space="preserve">OP_summon_JTFM_besides</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 내 덱에 있는 동아리 중 하나를 선택하여 입부합니다.</t>
+          <t xml:space="preserve">등교 : 자신의 양 옆에 '정의실현부 부원'을 소환합니다.</t>
         </is>
       </c>
       <c r="P58"/>
@@ -5175,12 +5201,12 @@
       <c r="S58"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Nakamasa_Ichika/Nakamasa_Ichika_Card.png</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Nakamasa_Ichika/Nakamasa_Ichika_Board.png</t>
         </is>
       </c>
       <c r="V58"/>
@@ -5199,49 +5225,53 @@
       <c r="C59"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">New_Club_Member_Tutorial</t>
+          <t xml:space="preserve">Nekozuka_Hibiki</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">신입 동아리원</t>
+          <t xml:space="preserve">네코즈카 히비키</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G59">
         <v>4</v>
       </c>
       <c r="H59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>3</v>
-      </c>
-      <c r="J59"/>
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering_Department</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L59"/>
       <c r="M59"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice_club</t>
+          <t xml:space="preserve">OP_damage1_X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 내 덱에 있는 동아리 중 하나를 선택하여 입부합니다.</t>
+          <t xml:space="preserve">등교 : 지정한 범위의 타일에 피해를 1 줍니다.</t>
         </is>
       </c>
       <c r="P59"/>
       <c r="Q59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59">
         <v>100</v>
@@ -5249,12 +5279,12 @@
       <c r="S59"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Card.png</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Board.png</t>
         </is>
       </c>
       <c r="V59"/>
@@ -5262,7 +5292,11 @@
       <c r="X59"/>
       <c r="Y59"/>
       <c r="Z59"/>
-      <c r="AA59"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Hibiki/Hibiki_CommonSkill.mp3</t>
+        </is>
+      </c>
       <c r="AB59"/>
       <c r="AC59"/>
       <c r="AD59"/>
@@ -5273,62 +5307,78 @@
       <c r="C60"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nonomi_Fire</t>
+          <t xml:space="preserve">Nekozuka_Hibiki_Tutorial</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">노노미, 총을 쏴</t>
+          <t xml:space="preserve">네코즈카 히비키</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering_Department</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L60"/>
       <c r="M60"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_damage1_all_enemy</t>
+          <t xml:space="preserve">OP_damage1_X;OG_taunt</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 적 유닛에게 피해를 1 줍니다.</t>
+          <t xml:space="preserve">등교 : 지정한 범위의 타일에 피해를 1 줍니다.</t>
         </is>
       </c>
       <c r="P60"/>
       <c r="Q60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60">
         <v>100</v>
       </c>
       <c r="S60"/>
-      <c r="T60"/>
-      <c r="U60"/>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Card.png</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Nekozuka_Hibiki/Nekozuka_Hibiki_Board.png</t>
+        </is>
+      </c>
       <c r="V60"/>
       <c r="W60"/>
       <c r="X60"/>
       <c r="Y60"/>
       <c r="Z60"/>
-      <c r="AA60"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Hibiki/Hibiki_CommonSkill.mp3</t>
+        </is>
+      </c>
       <c r="AB60"/>
       <c r="AC60"/>
       <c r="AD60"/>
@@ -5339,56 +5389,64 @@
       <c r="C61"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nonomi_Fire_Tutorial</t>
+          <t xml:space="preserve">New_Club_Member</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">노노미, 총을 쏴</t>
+          <t xml:space="preserve">신입 동아리원</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G61">
+        <v>4</v>
+      </c>
+      <c r="H61">
         <v>2</v>
       </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
       <c r="I61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L61"/>
       <c r="M61"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_damage1_all_enemy</t>
+          <t xml:space="preserve">choice_club</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve">모든 적 유닛에게 피해를 1 줍니다.</t>
+          <t xml:space="preserve">등교 : 내 덱에 있는 동아리 중 하나를 선택하여 입부합니다.</t>
         </is>
       </c>
       <c r="P61"/>
       <c r="Q61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61">
         <v>100</v>
       </c>
       <c r="S61"/>
-      <c r="T61"/>
-      <c r="U61"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Card.png</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Board.png</t>
+        </is>
+      </c>
       <c r="V61"/>
       <c r="W61"/>
       <c r="X61"/>
@@ -5405,44 +5463,44 @@
       <c r="C62"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">PA_Add_Mana_OPP_Hand_val_CM</t>
+          <t xml:space="preserve">New_Club_Member_Tutorial</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">PA_Add_Mana_OPP_Hand_val_CM</t>
+          <t xml:space="preserve">신입 동아리원</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">PlayerAbility</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L62"/>
       <c r="M62"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">OU_store_val_CM;OG_add_mana_opp_hand_event;SOT_OG_duration</t>
+          <t xml:space="preserve">choice_club</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신의 기계 수만큼 다음 턴 동안 상대의 이벤트 카드의 비용을 증가시킵니다.</t>
+          <t xml:space="preserve">등교 : 내 덱에 있는 동아리 중 하나를 선택하여 입부합니다.</t>
         </is>
       </c>
       <c r="P62"/>
@@ -5453,8 +5511,16 @@
         <v>100</v>
       </c>
       <c r="S62"/>
-      <c r="T62"/>
-      <c r="U62"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Card.png</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/New_Club_Memeber/New_Club_Member_Board.png</t>
+        </is>
+      </c>
       <c r="V62"/>
       <c r="W62"/>
       <c r="X62"/>
@@ -5471,49 +5537,49 @@
       <c r="C63"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan_Zzang</t>
+          <t xml:space="preserve">Nonomi_Fire</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">팬짱</t>
+          <t xml:space="preserve">노노미, 총을 쏴</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G63">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L63"/>
       <c r="M63"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_add_atk_hp_total_heal</t>
+          <t xml:space="preserve">spell_damage1_all_enemy</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve">이번 게임에서 아군이 받은 치유량만큼 체력과 공격력이 증가합니다.</t>
+          <t xml:space="preserve">모든 적 유닛에게 피해를 1 줍니다.</t>
         </is>
       </c>
       <c r="P63"/>
       <c r="Q63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63">
         <v>100</v>
@@ -5537,48 +5603,44 @@
       <c r="C64"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peroro_Tlush</t>
+          <t xml:space="preserve">Nonomi_Fire_Tutorial</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">페로로 인형</t>
+          <t xml:space="preserve">노노미, 총을 쏴</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
       <c r="I64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+          <t xml:space="preserve">NONE</t>
+        </is>
+      </c>
+      <c r="L64"/>
       <c r="M64"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_taunt</t>
+          <t xml:space="preserve">spell_damage1_all_enemy</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve">도발</t>
+          <t xml:space="preserve">모든 적 유닛에게 피해를 1 줍니다.</t>
         </is>
       </c>
       <c r="P64"/>
@@ -5607,17 +5669,17 @@
       <c r="C65"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pyroxene</t>
+          <t xml:space="preserve">PA_Add_Mana_OPP_Hand_val_CM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">청휘석</t>
+          <t xml:space="preserve">PA_Add_Mana_OPP_Hand_val_CM</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">PlayerAbility</t>
         </is>
       </c>
       <c r="G65">
@@ -5627,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65"/>
       <c r="K65" t="inlineStr">
@@ -5639,12 +5701,12 @@
       <c r="M65"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_coin</t>
+          <t xml:space="preserve">OU_store_val_CM;OG_add_mana_opp_hand_event;SOT_OG_duration</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve">청휘석을 하나 얻습니다.</t>
+          <t xml:space="preserve">자신의 기계 수만큼 다음 턴 동안 상대의 이벤트 카드의 비용을 증가시킵니다.</t>
         </is>
       </c>
       <c r="P65"/>
@@ -5655,11 +5717,7 @@
         <v>100</v>
       </c>
       <c r="S65"/>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Event/Pyroxene/Pyroxene_Card.png</t>
-        </is>
-      </c>
+      <c r="T65"/>
       <c r="U65"/>
       <c r="V65"/>
       <c r="W65"/>
@@ -5677,12 +5735,12 @@
       <c r="C66"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rampaging_Border_Drone</t>
+          <t xml:space="preserve">Pan_Zzang</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">폭주하는 드론</t>
+          <t xml:space="preserve">팬짱</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5691,13 +5749,13 @@
         </is>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66"/>
       <c r="K66" t="inlineStr">
@@ -5705,40 +5763,28 @@
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+      <c r="L66"/>
       <c r="M66"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_damage3_PS</t>
+          <t xml:space="preserve">OG_add_atk_hp_total_heal</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 자신의 선생님에게 피해를 3 줍니다.  </t>
+          <t xml:space="preserve">이번 게임에서 아군이 받은 치유량만큼 체력과 공격력이 증가합니다.</t>
         </is>
       </c>
       <c r="P66"/>
       <c r="Q66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66">
         <v>100</v>
       </c>
       <c r="S66"/>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Card.png</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Board.png</t>
-        </is>
-      </c>
+      <c r="T66"/>
+      <c r="U66"/>
       <c r="V66"/>
       <c r="W66"/>
       <c r="X66"/>
@@ -5755,12 +5801,12 @@
       <c r="C67"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rampaging_Border_Drone_Tutorial</t>
+          <t xml:space="preserve">Peroro_Tlush</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">폭주하는 드론</t>
+          <t xml:space="preserve">페로로 인형</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5769,10 +5815,10 @@
         </is>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I67">
         <v>2</v>
@@ -5791,12 +5837,12 @@
       <c r="M67"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_damage3_PS</t>
+          <t xml:space="preserve">OG_taunt</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 자신의 선생님에게 피해를 3 줍니다.  </t>
+          <t xml:space="preserve">도발</t>
         </is>
       </c>
       <c r="P67"/>
@@ -5807,16 +5853,8 @@
         <v>100</v>
       </c>
       <c r="S67"/>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Card.png</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Board.png</t>
-        </is>
-      </c>
+      <c r="T67"/>
+      <c r="U67"/>
       <c r="V67"/>
       <c r="W67"/>
       <c r="X67"/>
@@ -5833,17 +5871,17 @@
       <c r="C68"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">School_Lunch_Club</t>
+          <t xml:space="preserve">Pyroxene</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">급양부</t>
+          <t xml:space="preserve">청휘석</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G68">
@@ -5855,11 +5893,7 @@
       <c r="I68">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">School_Lunch_Club</t>
-        </is>
-      </c>
+      <c r="J68"/>
       <c r="K68" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE</t>
@@ -5869,12 +5903,12 @@
       <c r="M68"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUO_summon_CT;OUO_summon_PZ;OG_set_club_ui</t>
+          <t xml:space="preserve">spell_coin</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve">급양부 학생이 소환되면, 각 학생의 시그니처 소환물을 소환합니다.</t>
+          <t xml:space="preserve">청휘석을 하나 얻습니다.</t>
         </is>
       </c>
       <c r="P68"/>
@@ -5885,7 +5919,11 @@
         <v>100</v>
       </c>
       <c r="S68"/>
-      <c r="T68"/>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Event/Pyroxene/Pyroxene_Card.png</t>
+        </is>
+      </c>
       <c r="U68"/>
       <c r="V68"/>
       <c r="W68"/>
@@ -5903,44 +5941,48 @@
       <c r="C69"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scream_Rider</t>
+          <t xml:space="preserve">Rampaging_Border_Drone</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">스크림 라이더</t>
+          <t xml:space="preserve">폭주하는 드론</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G69">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
-        </is>
-      </c>
-      <c r="L69"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M69"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_damage4_row</t>
+          <t xml:space="preserve">OP_damage3_PS</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve">선택한 열의 모든 유닛에게 4의 피해를 준다.</t>
+          <t xml:space="preserve">등교 : 자신의 선생님에게 피해를 3 줍니다.  </t>
         </is>
       </c>
       <c r="P69"/>
@@ -5951,8 +5993,16 @@
         <v>100</v>
       </c>
       <c r="S69"/>
-      <c r="T69"/>
-      <c r="U69"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Card.png</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Board.png</t>
+        </is>
+      </c>
       <c r="V69"/>
       <c r="W69"/>
       <c r="X69"/>
@@ -5969,56 +6019,68 @@
       <c r="C70"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scry_Keep</t>
+          <t xml:space="preserve">Rampaging_Border_Drone_Tutorial</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">밑으로 내리기</t>
+          <t xml:space="preserve">폭주하는 드론</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J70"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
-        </is>
-      </c>
-      <c r="L70"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M70"/>
-      <c r="N70"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP_damage3_PS</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve">이 카드를 고르면 덱 맨 위 카드를 맨 아래로 보냅니다.</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이 카드를 고르면 덱 맨 위 카드를 맨 아래로 보냅니다.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">등교 : 자신의 선생님에게 피해를 3 줍니다.  </t>
+        </is>
+      </c>
+      <c r="P70"/>
       <c r="Q70">
         <v>0</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S70"/>
-      <c r="T70"/>
-      <c r="U70"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Card.png</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Rampaging_Border_Drone/Rampaging_Border_Drone_Board.png</t>
+        </is>
+      </c>
       <c r="V70"/>
       <c r="W70"/>
       <c r="X70"/>
@@ -6035,27 +6097,27 @@
       <c r="C71"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shiba_Seki_Ramen</t>
+          <t xml:space="preserve">Recall_Order</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">시바세키 라멘집</t>
+          <t xml:space="preserve">귀가 명령</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J71"/>
       <c r="K71" t="inlineStr">
@@ -6067,13 +6129,21 @@
       <c r="M71"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OD_summon_SSRFS</t>
-        </is>
-      </c>
-      <c r="O71"/>
-      <c r="P71"/>
+          <t xml:space="preserve">spell_bounce_enemy</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지정한 적 1명을 상대의 손으로 되돌립니다.</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지정한 적 1명을 상대의 손으로 되돌립니다.</t>
+        </is>
+      </c>
       <c r="Q71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71">
         <v>100</v>
@@ -6097,41 +6167,49 @@
       <c r="C72"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shiba_Seki_Ramen_Food_Stall</t>
+          <t xml:space="preserve">Riot_Shield_Trooper</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">시바세키 라멘집</t>
+          <t xml:space="preserve">방패 진압병</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J72"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L72"/>
       <c r="M72"/>
-      <c r="N72"/>
-      <c r="O72"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OAA_knockback1</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">넉백</t>
+        </is>
+      </c>
       <c r="P72"/>
       <c r="Q72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72">
         <v>100</v>
@@ -6155,29 +6233,33 @@
       <c r="C73"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shiba_Seki_Ramen_Food_Stall_Tutorial</t>
+          <t xml:space="preserve">School_Lunch_Club</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">시바세키 라멘집</t>
+          <t xml:space="preserve">급양부</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">Club</t>
         </is>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
       <c r="I73">
-        <v>2</v>
-      </c>
-      <c r="J73"/>
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School_Lunch_Club</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE</t>
@@ -6185,8 +6267,16 @@
       </c>
       <c r="L73"/>
       <c r="M73"/>
-      <c r="N73"/>
-      <c r="O73"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OUO_summon_CT;OUO_summon_PZ;OG_set_club_ui</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">급양부 학생이 소환되면, 각 학생의 시그니처 소환물을 소환합니다.</t>
+        </is>
+      </c>
       <c r="P73"/>
       <c r="Q73">
         <v>0</v>
@@ -6213,27 +6303,27 @@
       <c r="C74"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shiba_Seki_Ramen_Tutorial</t>
+          <t xml:space="preserve">Scream_Rider</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">시바세키 라멘집</t>
+          <t xml:space="preserve">스크림 라이더</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74"/>
       <c r="K74" t="inlineStr">
@@ -6245,13 +6335,17 @@
       <c r="M74"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OD_summon_SSRFS_Tutorial</t>
-        </is>
-      </c>
-      <c r="O74"/>
+          <t xml:space="preserve">spell_damage4_row</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택한 열의 모든 유닛에게 4의 피해를 준다.</t>
+        </is>
+      </c>
       <c r="P74"/>
       <c r="Q74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74">
         <v>100</v>
@@ -6275,68 +6369,56 @@
       <c r="C75"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shimoe_Koharu</t>
+          <t xml:space="preserve">Scry_Keep</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">시모에 코하루</t>
+          <t xml:space="preserve">밑으로 내리기</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Make_Up_Work_Club;Justice_Task_Force</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J75"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L75"/>
       <c r="M75"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPO_SH_add_hp1</t>
-        </is>
-      </c>
+      <c r="N75"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">'수상한 하니와'를 사용하면 체력이 1 증가합니다.</t>
-        </is>
-      </c>
-      <c r="P75"/>
+          <t xml:space="preserve">이 카드를 고르면 덱 맨 위 카드를 맨 아래로 보냅니다.</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이 카드를 고르면 덱 맨 위 카드를 맨 아래로 보냅니다.</t>
+        </is>
+      </c>
       <c r="Q75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S75"/>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shimoe_Koharu/Shimoe_Koharu_Card.png</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shimoe_Koharu/Shimoe_Koharu_Board.png</t>
-        </is>
-      </c>
+      <c r="T75"/>
+      <c r="U75"/>
       <c r="V75"/>
       <c r="W75"/>
       <c r="X75"/>
@@ -6353,50 +6435,42 @@
       <c r="C76"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shimokura_Megu</t>
+          <t xml:space="preserve">Sentry_Robot</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">시모쿠라 메구</t>
+          <t xml:space="preserve">경비 로봇</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G76">
         <v>2</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I76">
-        <v>3</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hot_Springs_Department</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J76"/>
       <c r="K76" t="inlineStr">
         <is>
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L76"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M76"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OAA_Damage1_LA_neighborslot</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공격한 유닛 주변 1칸의 타일에도 피해를 1 줍니다.</t>
-        </is>
-      </c>
+      <c r="N76"/>
+      <c r="O76"/>
       <c r="P76"/>
       <c r="Q76">
         <v>1</v>
@@ -6405,26 +6479,14 @@
         <v>100</v>
       </c>
       <c r="S76"/>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Shimokura_Megu/Shimokura_Megu_Card.png</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Shimokura_Megu/Shimokura_Megu_Board.png</t>
-        </is>
-      </c>
+      <c r="T76"/>
+      <c r="U76"/>
       <c r="V76"/>
       <c r="W76"/>
       <c r="X76"/>
       <c r="Y76"/>
       <c r="Z76"/>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Gehenna/Hot_Spring_Department/Megu/Megu_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA76"/>
       <c r="AB76"/>
       <c r="AC76"/>
       <c r="AD76"/>
@@ -6435,50 +6497,42 @@
       <c r="C77"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shiraishi_Utaha</t>
+          <t xml:space="preserve">Shiba_Seki_Ramen</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">시라이시 우타하</t>
+          <t xml:space="preserve">시바세키 라멘집</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G77">
         <v>2</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77">
-        <v>3</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J77"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L77"/>
       <c r="M77"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">play_summon_thundergun</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">등교 : 주변 1칸의 타일 중 선택하여 '천둥이' (1/1)를 소환합니다.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">OD_summon_SSRFS</t>
+        </is>
+      </c>
+      <c r="O77"/>
       <c r="P77"/>
       <c r="Q77">
         <v>1</v>
@@ -6487,26 +6541,14 @@
         <v>100</v>
       </c>
       <c r="S77"/>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Card.png</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Board.png</t>
-        </is>
-      </c>
+      <c r="T77"/>
+      <c r="U77"/>
       <c r="V77"/>
       <c r="W77"/>
       <c r="X77"/>
       <c r="Y77"/>
       <c r="Z77"/>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Utaha/Utaha_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA77"/>
       <c r="AB77"/>
       <c r="AC77"/>
       <c r="AD77"/>
@@ -6517,50 +6559,38 @@
       <c r="C78"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shiraishi_Utaha_Tutorial</t>
+          <t xml:space="preserve">Shiba_Seki_Ramen_Food_Stall</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">시라이시 우타하</t>
+          <t xml:space="preserve">시바세키 라멘집</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
         <v>2</v>
       </c>
-      <c r="H78">
-        <v>1</v>
-      </c>
-      <c r="I78">
-        <v>3</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+      <c r="J78"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L78"/>
       <c r="M78"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">play_summon_thundergun_Tutorial</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">등교 : 주변 1칸의 타일 중 선택하여 '천둥이' (1/1)를 소환합니다.</t>
-        </is>
-      </c>
+      <c r="N78"/>
+      <c r="O78"/>
       <c r="P78"/>
       <c r="Q78">
         <v>0</v>
@@ -6569,26 +6599,14 @@
         <v>100</v>
       </c>
       <c r="S78"/>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Card.png</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Board.png</t>
-        </is>
-      </c>
+      <c r="T78"/>
+      <c r="U78"/>
       <c r="V78"/>
       <c r="W78"/>
       <c r="X78"/>
       <c r="Y78"/>
       <c r="Z78"/>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Utaha/Utaha_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA78"/>
       <c r="AB78"/>
       <c r="AC78"/>
       <c r="AD78"/>
@@ -6599,68 +6617,48 @@
       <c r="C79"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shirasu_Azusa</t>
+          <t xml:space="preserve">Shiba_Seki_Ramen_Food_Stall_Tutorial</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">시라스 아즈사</t>
+          <t xml:space="preserve">시바세키 라멘집</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G79">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79">
-        <v>4</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Make_Up_Work_Club;Arius_Squad</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J79"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L79"/>
       <c r="M79"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OP_create_self_HDB</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">등교 : '헤일로를 파괴하는 폭탄'을 손으로 가져옵니다.</t>
-        </is>
-      </c>
+      <c r="N79"/>
+      <c r="O79"/>
       <c r="P79"/>
       <c r="Q79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79">
         <v>100</v>
       </c>
       <c r="S79"/>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shirasu_Azusa/Shirasu_Azusa_Card.png</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shirasu_Azusa/Shirasu_Azusa_Board.png</t>
-        </is>
-      </c>
+      <c r="T79"/>
+      <c r="U79"/>
       <c r="V79"/>
       <c r="W79"/>
       <c r="X79"/>
@@ -6677,46 +6675,42 @@
       <c r="C80"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shishido_Izumi</t>
+          <t xml:space="preserve">Shiba_Seki_Ramen_Tutorial</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">시시도우 이즈미</t>
+          <t xml:space="preserve">시바세키 라멘집</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
         <v>4</v>
       </c>
-      <c r="H80">
-        <v>4</v>
-      </c>
-      <c r="I80">
-        <v>5</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gourmet_Research_Society</t>
-        </is>
-      </c>
+      <c r="J80"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L80"/>
       <c r="M80"/>
-      <c r="N80"/>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자신이 받는 효과 데미지를 회복으로 받습니다.</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OD_summon_SSRFS_Tutorial</t>
+        </is>
+      </c>
+      <c r="O80"/>
       <c r="P80"/>
       <c r="Q80">
         <v>0</v>
@@ -6743,12 +6737,12 @@
       <c r="C81"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shizuyama_Mashiro</t>
+          <t xml:space="preserve">Shimoe_Koharu</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">시즈야마 마시로</t>
+          <t xml:space="preserve">시모에 코하루</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6757,17 +6751,17 @@
         </is>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Justice_Task_Force</t>
+          <t xml:space="preserve">Make_Up_Work_Club;Justice_Task_Force</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6779,12 +6773,12 @@
       <c r="M81"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">OAA_damage_0.5</t>
+          <t xml:space="preserve">OPO_SH_add_hp1</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">50% 확률로 공격한 적을 다시 공격합니다.</t>
+          <t xml:space="preserve">'수상한 하니와'를 사용하면 체력이 1 증가합니다.</t>
         </is>
       </c>
       <c r="P81"/>
@@ -6797,12 +6791,12 @@
       <c r="S81"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Shizuyama_Mashiro/Shizuyama_Mashiro_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shimoe_Koharu/Shimoe_Koharu_Card.png</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Shizuyama_Mashiro/Shizuyama_Mashiro_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shimoe_Koharu/Shimoe_Koharu_Board.png</t>
         </is>
       </c>
       <c r="V81"/>
@@ -6821,44 +6815,48 @@
       <c r="C82"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student_Council_Supply</t>
+          <t xml:space="preserve">Shimokura_Megu</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">학생회 보급</t>
+          <t xml:space="preserve">시모쿠라 메구</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
         <v>3</v>
       </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hot_Springs_Department</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L82"/>
       <c r="M82"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">spell_draw2</t>
+          <t xml:space="preserve">OAA_Damage1_LA_neighborslot</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">카드를 2장 뽑습니다.</t>
+          <t xml:space="preserve">공격한 유닛 주변 1칸의 타일에도 피해를 1 줍니다.</t>
         </is>
       </c>
       <c r="P82"/>
@@ -6869,14 +6867,26 @@
         <v>100</v>
       </c>
       <c r="S82"/>
-      <c r="T82"/>
-      <c r="U82"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Shimokura_Megu/Shimokura_Megu_Card.png</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Hot_Spring_Department/Shimokura_Megu/Shimokura_Megu_Board.png</t>
+        </is>
+      </c>
       <c r="V82"/>
       <c r="W82"/>
       <c r="X82"/>
       <c r="Y82"/>
       <c r="Z82"/>
-      <c r="AA82"/>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Gehenna/Hot_Spring_Department/Megu/Megu_CommonSkill.mp3</t>
+        </is>
+      </c>
       <c r="AB82"/>
       <c r="AC82"/>
       <c r="AD82"/>
@@ -6887,58 +6897,78 @@
       <c r="C83"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suspicious_Haniwa</t>
+          <t xml:space="preserve">Shiraishi_Utaha</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">수상한 하니와</t>
+          <t xml:space="preserve">시라이시 우타하</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83">
-        <v>0</v>
-      </c>
-      <c r="J83"/>
+        <v>3</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering_Department</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L83"/>
       <c r="M83"/>
-      <c r="N83"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">play_summon_thundergun</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">수상합니다....</t>
+          <t xml:space="preserve">등교 : 주변 1칸의 타일 중 선택하여 '천둥이' (1/1)를 소환합니다.</t>
         </is>
       </c>
       <c r="P83"/>
       <c r="Q83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83">
         <v>100</v>
       </c>
       <c r="S83"/>
-      <c r="T83"/>
-      <c r="U83"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Card.png</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Board.png</t>
+        </is>
+      </c>
       <c r="V83"/>
       <c r="W83"/>
       <c r="X83"/>
       <c r="Y83"/>
       <c r="Z83"/>
-      <c r="AA83"/>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Utaha/Utaha_CommonSkill.mp3</t>
+        </is>
+      </c>
       <c r="AB83"/>
       <c r="AC83"/>
       <c r="AD83"/>
@@ -6949,53 +6979,53 @@
       <c r="C84"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweeper</t>
+          <t xml:space="preserve">Shiraishi_Utaha_Tutorial</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">스위퍼</t>
+          <t xml:space="preserve">시라이시 우타하</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>1</v>
-      </c>
-      <c r="J84"/>
+        <v>3</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering_Department</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+      <c r="L84"/>
       <c r="M84"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">OU_haste</t>
+          <t xml:space="preserve">play_summon_thundergun_Tutorial</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">속사</t>
+          <t xml:space="preserve">등교 : 주변 1칸의 타일 중 선택하여 '천둥이' (1/1)를 소환합니다.</t>
         </is>
       </c>
       <c r="P84"/>
       <c r="Q84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84">
         <v>100</v>
@@ -7003,12 +7033,12 @@
       <c r="S84"/>
       <c r="T84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Card.png</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/Shiraishi_Utahaa/Shiraishi_Utaha_Board.png</t>
         </is>
       </c>
       <c r="V84"/>
@@ -7016,7 +7046,11 @@
       <c r="X84"/>
       <c r="Y84"/>
       <c r="Z84"/>
-      <c r="AA84"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Utaha/Utaha_CommonSkill.mp3</t>
+        </is>
+      </c>
       <c r="AB84"/>
       <c r="AC84"/>
       <c r="AD84"/>
@@ -7027,53 +7061,53 @@
       <c r="C85"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweeper_Tutorial</t>
+          <t xml:space="preserve">Shirasu_Azusa</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">스위퍼</t>
+          <t xml:space="preserve">시라스 아즈사</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>1</v>
-      </c>
-      <c r="J85"/>
+        <v>4</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Make_Up_Work_Club;Arius_Squad</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MIDDLE</t>
+        </is>
+      </c>
+      <c r="L85"/>
       <c r="M85"/>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">OU_haste;OG_taunt</t>
+          <t xml:space="preserve">OP_create_self_HDB</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">속사</t>
+          <t xml:space="preserve">등교 : '헤일로를 파괴하는 폭탄'을 손으로 가져옵니다.</t>
         </is>
       </c>
       <c r="P85"/>
       <c r="Q85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85">
         <v>100</v>
@@ -7081,12 +7115,12 @@
       <c r="S85"/>
       <c r="T85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shirasu_Azusa/Shirasu_Azusa_Card.png</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Shirasu_Azusa/Shirasu_Azusa_Board.png</t>
         </is>
       </c>
       <c r="V85"/>
@@ -7105,44 +7139,44 @@
       <c r="C86"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Target_Delete</t>
+          <t xml:space="preserve">Shishido_Izumi</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">타겟, 제거</t>
+          <t xml:space="preserve">시시도우 이즈미</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spell</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G86">
+        <v>4</v>
+      </c>
+      <c r="H86">
+        <v>4</v>
+      </c>
+      <c r="I86">
         <v>5</v>
       </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gourmet_Research_Society</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L86"/>
       <c r="M86"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spell_damage10</t>
-        </is>
-      </c>
+      <c r="N86"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve">지정한 대상에게 피해를 10 줍니다.</t>
+          <t xml:space="preserve">자신이 받는 효과 데미지를 회복으로 받습니다.</t>
         </is>
       </c>
       <c r="P86"/>
@@ -7153,8 +7187,16 @@
         <v>100</v>
       </c>
       <c r="S86"/>
-      <c r="T86"/>
-      <c r="U86"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Shishido_Izumi/Shishido_Izumi_Card.png</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Shishido_Izumi/Shishido_Izumi_Board.png</t>
+        </is>
+      </c>
       <c r="V86"/>
       <c r="W86"/>
       <c r="X86"/>
@@ -7171,69 +7213,68 @@
       <c r="C87"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tea_Party</t>
+          <t xml:space="preserve">Shizuyama_Mashiro</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">티파티</t>
+          <t xml:space="preserve">시즈야마 마시로</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tea_Party</t>
+          <t xml:space="preserve">Justice_Task_Force</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L87"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tea_party_host=-1</t>
-        </is>
-      </c>
+      <c r="M87"/>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">AD_OGS_Summon_Tea_Party;SOT_TeaPartyHost;SOT_TeaPartyBuff</t>
+          <t xml:space="preserve">OAA_damage_0.5</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve">게임 시작 시, 티파티 부원을 모두 소환합니다. 자신의 차례 시작 시, 호스트가 바뀝니다.</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">게임 시작 시, 티파티 부원을 모두 소환합니다. 자신의 차례 시작 시, 호스트가 바뀝니다.
-현재 호스트는 {0} 입니다.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">50% 확률로 공격한 적을 다시 공격합니다.</t>
+        </is>
+      </c>
+      <c r="P87"/>
       <c r="Q87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87">
         <v>100</v>
       </c>
       <c r="S87"/>
-      <c r="T87"/>
-      <c r="U87"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Shizuyama_Mashiro/Shizuyama_Mashiro_Card.png</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Justice_Task_Force/Shizuyama_Mashiro/Shizuyama_Mashiro_Board.png</t>
+        </is>
+      </c>
       <c r="V87"/>
       <c r="W87"/>
       <c r="X87"/>
@@ -7250,27 +7291,27 @@
       <c r="C88"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tea_Party_Mainsion</t>
+          <t xml:space="preserve">Student_Council_Supply</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">티파티 별장</t>
+          <t xml:space="preserve">학생회 보급</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G88">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J88"/>
       <c r="K88" t="inlineStr">
@@ -7280,8 +7321,16 @@
       </c>
       <c r="L88"/>
       <c r="M88"/>
-      <c r="N88"/>
-      <c r="O88"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spell_draw2</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카드를 2장 뽑습니다.</t>
+        </is>
+      </c>
       <c r="P88"/>
       <c r="Q88">
         <v>1</v>
@@ -7308,12 +7357,12 @@
       <c r="C89"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test_Heal</t>
+          <t xml:space="preserve">Suspicious_Haniwa</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">테스트 힐</t>
+          <t xml:space="preserve">수상한 하니와</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7338,12 +7387,12 @@
       </c>
       <c r="L89"/>
       <c r="M89"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spell_heal_full</t>
-        </is>
-      </c>
-      <c r="O89"/>
+      <c r="N89"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수상합니다....</t>
+        </is>
+      </c>
       <c r="P89"/>
       <c r="Q89">
         <v>0</v>
@@ -7370,12 +7419,12 @@
       <c r="C90"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">The_Avant_Guard</t>
+          <t xml:space="preserve">Sweeper</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">아방가르드군</t>
+          <t xml:space="preserve">스위퍼</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7384,13 +7433,13 @@
         </is>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90"/>
       <c r="K90" t="inlineStr">
@@ -7422,8 +7471,16 @@
         <v>100</v>
       </c>
       <c r="S90"/>
-      <c r="T90"/>
-      <c r="U90"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Card.png</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Board.png</t>
+        </is>
+      </c>
       <c r="V90"/>
       <c r="W90"/>
       <c r="X90"/>
@@ -7440,49 +7497,53 @@
       <c r="C91"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">The_Way_To_School</t>
+          <t xml:space="preserve">Sweeper_Tutorial</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교길</t>
+          <t xml:space="preserve">스위퍼</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J91"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
-        </is>
-      </c>
-      <c r="L91"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M91"/>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT_create_Hand_CS</t>
+          <t xml:space="preserve">OU_haste;OG_taunt</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신의 턴 시작 시, '등교생' (1/1)을 패로 가져옵니다.</t>
+          <t xml:space="preserve">속사</t>
         </is>
       </c>
       <c r="P91"/>
       <c r="Q91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91">
         <v>100</v>
@@ -7490,12 +7551,12 @@
       <c r="S91"/>
       <c r="T91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Card.png</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Sweeper/Sweeper_Board.png</t>
         </is>
       </c>
       <c r="V91"/>
@@ -7514,27 +7575,27 @@
       <c r="C92"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">The_Way_To_School_Tutorial</t>
+          <t xml:space="preserve">Target_Delete</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교길</t>
+          <t xml:space="preserve">타겟, 제거</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H92">
         <v>0</v>
       </c>
       <c r="I92">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J92"/>
       <c r="K92" t="inlineStr">
@@ -7546,32 +7607,24 @@
       <c r="M92"/>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT_create_Hand_CS</t>
+          <t xml:space="preserve">spell_damage10</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신의 턴 시작 시, '등교생' (1/1)을 패로 가져옵니다.</t>
+          <t xml:space="preserve">지정한 대상에게 피해를 10 줍니다.</t>
         </is>
       </c>
       <c r="P92"/>
       <c r="Q92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92">
         <v>100</v>
       </c>
       <c r="S92"/>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Card.png</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Board.png</t>
-        </is>
-      </c>
+      <c r="T92"/>
+      <c r="U92"/>
       <c r="V92"/>
       <c r="W92"/>
       <c r="X92"/>
@@ -7588,43 +7641,60 @@
       <c r="C93"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thundergun</t>
+          <t xml:space="preserve">Tea_Party</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">천둥이</t>
+          <t xml:space="preserve">티파티</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Club</t>
         </is>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>1</v>
-      </c>
-      <c r="J93"/>
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tea_Party</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
-      <c r="M93"/>
-      <c r="N93"/>
-      <c r="O93"/>
-      <c r="P93"/>
+          <t xml:space="preserve">NONE</t>
+        </is>
+      </c>
+      <c r="L93"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tea_party_host=-1</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD_OGS_Summon_Tea_Party;SOT_TeaPartyHost;SOT_TeaPartyBuff</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게임 시작 시, 티파티 부원을 모두 소환합니다. 자신의 차례 시작 시, 호스트가 바뀝니다.</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게임 시작 시, 티파티 부원을 모두 소환합니다. 자신의 차례 시작 시, 호스트가 바뀝니다.
+현재 호스트는 {0} 입니다.</t>
+        </is>
+      </c>
       <c r="Q93">
         <v>0</v>
       </c>
@@ -7632,16 +7702,8 @@
         <v>100</v>
       </c>
       <c r="S93"/>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Card.png</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Board.png</t>
-        </is>
-      </c>
+      <c r="T93"/>
+      <c r="U93"/>
       <c r="V93"/>
       <c r="W93"/>
       <c r="X93"/>
@@ -7658,60 +7720,48 @@
       <c r="C94"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thundergun_Tutorial</t>
+          <t xml:space="preserve">Tea_Party_Mainsion</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">천둥이</t>
+          <t xml:space="preserve">티파티 별장</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">NonStudent</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G94">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J94"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+          <t xml:space="preserve">NONE</t>
+        </is>
+      </c>
+      <c r="L94"/>
       <c r="M94"/>
       <c r="N94"/>
       <c r="O94"/>
       <c r="P94"/>
       <c r="Q94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94">
         <v>100</v>
       </c>
       <c r="S94"/>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Card.png</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Board.png</t>
-        </is>
-      </c>
+      <c r="T94"/>
+      <c r="U94"/>
       <c r="V94"/>
       <c r="W94"/>
       <c r="X94"/>
@@ -7728,78 +7778,58 @@
       <c r="C95"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toyomi_Kotori</t>
+          <t xml:space="preserve">Test_Heal</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">토요미 코토리</t>
+          <t xml:space="preserve">테스트 힐</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Spell</t>
         </is>
       </c>
       <c r="G95">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95">
-        <v>2</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J95"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L95"/>
       <c r="M95"/>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">OUO_summon_machine_draw_card</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기계를 소환 시, 선생님에게 피해를 1 입히고 속사를 부여합니다.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">spell_heal_full</t>
+        </is>
+      </c>
+      <c r="O95"/>
       <c r="P95"/>
       <c r="Q95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95">
         <v>100</v>
       </c>
       <c r="S95"/>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/kotori_card.png</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/Kotori_Board.png</t>
-        </is>
-      </c>
+      <c r="T95"/>
+      <c r="U95"/>
       <c r="V95"/>
       <c r="W95"/>
       <c r="X95"/>
       <c r="Y95"/>
       <c r="Z95"/>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Kotori/Kotori_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA95"/>
       <c r="AB95"/>
       <c r="AC95"/>
       <c r="AD95"/>
@@ -7810,44 +7840,48 @@
       <c r="C96"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toyomi_Kotori_Tutorial</t>
+          <t xml:space="preserve">The_Avant_Guard</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">토요미 코토리</t>
+          <t xml:space="preserve">아방가르드군</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G96">
+        <v>5</v>
+      </c>
+      <c r="H96">
         <v>4</v>
-      </c>
-      <c r="H96">
-        <v>1</v>
       </c>
       <c r="I96">
         <v>2</v>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering_Department</t>
-        </is>
-      </c>
+      <c r="J96"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
-        </is>
-      </c>
-      <c r="L96"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M96"/>
-      <c r="N96"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OU_haste</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 다음 상대 턴까지 아군 기계 수만큼 상대 이벤트 카드의 비용이 증가합니다.</t>
+          <t xml:space="preserve">속사</t>
         </is>
       </c>
       <c r="P96"/>
@@ -7858,26 +7892,14 @@
         <v>100</v>
       </c>
       <c r="S96"/>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/kotori_card.png</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/Kotori_Board.png</t>
-        </is>
-      </c>
+      <c r="T96"/>
+      <c r="U96"/>
       <c r="V96"/>
       <c r="W96"/>
       <c r="X96"/>
       <c r="Y96"/>
       <c r="Z96"/>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Kotori/Kotori_CommonSkill.mp3</t>
-        </is>
-      </c>
+      <c r="AA96"/>
       <c r="AB96"/>
       <c r="AC96"/>
       <c r="AD96"/>
@@ -7888,33 +7910,29 @@
       <c r="C97"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
+          <t xml:space="preserve">The_Way_To_School</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">트리니티 자경단</t>
+          <t xml:space="preserve">등교길</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Club</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97">
         <v>0</v>
       </c>
       <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J97"/>
       <c r="K97" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE</t>
@@ -7924,17 +7942,17 @@
       <c r="M97"/>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">OG_set_club_ui</t>
+          <t xml:space="preserve">SOT_create_Hand_CS</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve">사거리 내에 적 유닛이 있어도, 선생님을 우선 공격합니다.</t>
+          <t xml:space="preserve">자신의 턴 시작 시, '등교생' (1/1)을 패로 가져옵니다.</t>
         </is>
       </c>
       <c r="P97"/>
       <c r="Q97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97">
         <v>100</v>
@@ -7942,12 +7960,12 @@
       <c r="S97"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Trinity/Trinity_Vigilante_Crew_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Card.png</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Trinity/Trinity_Vigilante_Crew_Icon.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Board.png</t>
         </is>
       </c>
       <c r="V97"/>
@@ -7966,53 +7984,49 @@
       <c r="C98"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tsuchinaga_Hiyori</t>
+          <t xml:space="preserve">The_Way_To_School_Tutorial</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">츠치나가 히요리</t>
+          <t xml:space="preserve">등교길</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Place</t>
         </is>
       </c>
       <c r="G98">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Arius_Squad</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J98"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L98"/>
       <c r="M98"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT_usemana1_PS_draw</t>
+          <t xml:space="preserve">SOT_create_Hand_CS</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve">자신의 차례 시작 시, 마나를 하나 제거하고 카드를 한 장 뽑습니다.</t>
+          <t xml:space="preserve">자신의 턴 시작 시, '등교생' (1/1)을 패로 가져옵니다.</t>
         </is>
       </c>
       <c r="P98"/>
       <c r="Q98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98">
         <v>100</v>
@@ -8020,12 +8034,12 @@
       <c r="S98"/>
       <c r="T98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Tsuchinaga_Hiyori/Tsuchinaga_Hiyori_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Card.png</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Tsuchinaga_Hiyori/Tsuchinaga_Hiyori_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Place/The_Way_To_School/The_Way_To_School_Board.png</t>
         </is>
       </c>
       <c r="V98"/>
@@ -8044,53 +8058,45 @@
       <c r="C99"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Urawa_Hanako</t>
+          <t xml:space="preserve">Thundergun</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">우라와 하나코</t>
+          <t xml:space="preserve">천둥이</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G99">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H99">
         <v>1</v>
       </c>
       <c r="I99">
-        <v>4</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Make_Up_Work_Club</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J99"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
-        </is>
-      </c>
-      <c r="L99"/>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M99"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OP_create_SH3</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">등교 : '수상한 하니와' 3장을 패로 가져옵니다.</t>
-        </is>
-      </c>
+      <c r="N99"/>
+      <c r="O99"/>
       <c r="P99"/>
       <c r="Q99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99">
         <v>100</v>
@@ -8098,12 +8104,12 @@
       <c r="S99"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Urawa_Hanako/Urawa_Hanako_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Card.png</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Urawa_Hanako/Urawa_Hanako_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Board.png</t>
         </is>
       </c>
       <c r="V99"/>
@@ -8122,50 +8128,42 @@
       <c r="C100"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ushimaki_Juri</t>
+          <t xml:space="preserve">Thundergun_Tutorial</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">우시마키 주리</t>
+          <t xml:space="preserve">천둥이</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">NonStudent</t>
         </is>
       </c>
       <c r="G100">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I100">
-        <v>5</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">School_Lunch_Club</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J100"/>
       <c r="K100" t="inlineStr">
         <is>
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L100"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">machine</t>
+        </is>
+      </c>
       <c r="M100"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OBA_exhaust_damage</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공격하는 대신 사거리 내의 모든 유닛에게 자신의 공격력만큼 피해를 줍니다.</t>
-        </is>
-      </c>
+      <c r="N100"/>
+      <c r="O100"/>
       <c r="P100"/>
       <c r="Q100">
         <v>0</v>
@@ -8174,8 +8172,16 @@
         <v>100</v>
       </c>
       <c r="S100"/>
-      <c r="T100"/>
-      <c r="U100"/>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Card.png</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Non_Student/Thundergun/Thundergun_Board.png</t>
+        </is>
+      </c>
       <c r="V100"/>
       <c r="W100"/>
       <c r="X100"/>
@@ -8192,12 +8198,12 @@
       <c r="C101"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uzawa_Reisa</t>
+          <t xml:space="preserve">Toyomi_Kotori</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">우자와 레이사</t>
+          <t xml:space="preserve">토요미 코토리</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8206,34 +8212,34 @@
         </is>
       </c>
       <c r="G101">
+        <v>4</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
         <v>2</v>
       </c>
-      <c r="H101">
-        <v>1</v>
-      </c>
-      <c r="I101">
-        <v>4</v>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
+          <t xml:space="preserve">Engineering_Department</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L101"/>
       <c r="M101"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP_move_enemy</t>
+          <t xml:space="preserve">OUO_summon_machine_draw_card</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 상대 유닛을 지정합니다. 해당 유닛을 이 유닛의 사거리 내의 원하는 타일로 이동시킵니다,</t>
+          <t xml:space="preserve">기계를 소환 시, 선생님에게 피해를 1 입히고 속사를 부여합니다.</t>
         </is>
       </c>
       <c r="P101"/>
@@ -8246,12 +8252,12 @@
       <c r="S101"/>
       <c r="T101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Uzawa_Reisa/Uzawa_Reisa_Card.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/kotori_card.png</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Uzawa_Reisa/Uzawa_Reisa_Board.png</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/Kotori_Board.png</t>
         </is>
       </c>
       <c r="V101"/>
@@ -8261,7 +8267,7 @@
       <c r="Z101"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Trinity/Trinity_Vigilante_Crew/Reisa/Reisa_CommonSkill.mp3</t>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Kotori/Kotori_CommonSkill.mp3</t>
         </is>
       </c>
       <c r="AB101"/>
@@ -8274,12 +8280,12 @@
       <c r="C102"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wanibuchi_Akari</t>
+          <t xml:space="preserve">Toyomi_Kotori_Tutorial</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">와니부치 아카리</t>
+          <t xml:space="preserve">토요미 코토리</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8288,34 +8294,30 @@
         </is>
       </c>
       <c r="G102">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I102">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gourmet_Research_Society</t>
+          <t xml:space="preserve">Engineering_Department</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L102"/>
       <c r="M102"/>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OP_damage_self_7</t>
-        </is>
-      </c>
+      <c r="N102"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t xml:space="preserve">등교 : 자기 자신에게 7 피해를 줍니다.</t>
+          <t xml:space="preserve">등교 : 다음 상대 턴까지 아군 기계 수만큼 상대 이벤트 카드의 비용이 증가합니다.</t>
         </is>
       </c>
       <c r="P102"/>
@@ -8326,14 +8328,26 @@
         <v>100</v>
       </c>
       <c r="S102"/>
-      <c r="T102"/>
-      <c r="U102"/>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/kotori_card.png</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Millenium/Engineering_Department/kotori/Kotori_Board.png</t>
+        </is>
+      </c>
       <c r="V102"/>
       <c r="W102"/>
       <c r="X102"/>
       <c r="Y102"/>
       <c r="Z102"/>
-      <c r="AA102"/>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Millenium/Engineering_Department/Kotori/Kotori_CommonSkill.mp3</t>
+        </is>
+      </c>
       <c r="AB102"/>
       <c r="AC102"/>
       <c r="AD102"/>
@@ -8344,60 +8358,68 @@
       <c r="C103"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yurizono_Seia</t>
+          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">유리조노 세이아</t>
+          <t xml:space="preserve">트리니티 자경단</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student</t>
+          <t xml:space="preserve">Club</t>
         </is>
       </c>
       <c r="G103">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H103">
         <v>0</v>
       </c>
       <c r="I103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tea_Party</t>
+          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIDDLE</t>
+          <t xml:space="preserve">NONE</t>
         </is>
       </c>
       <c r="L103"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tea_party_host=0</t>
-        </is>
-      </c>
+      <c r="M103"/>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOT_ScryTop_Create</t>
-        </is>
-      </c>
-      <c r="O103"/>
+          <t xml:space="preserve">OG_set_club_ui</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사거리 내에 적 유닛이 있어도, 선생님을 우선 공격합니다.</t>
+        </is>
+      </c>
       <c r="P103"/>
       <c r="Q103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103">
         <v>100</v>
       </c>
       <c r="S103"/>
-      <c r="T103"/>
-      <c r="U103"/>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Club/Trinity/Trinity_Vigilante_Crew_Card.png</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Clubs/Trinity/Trinity_Vigilante_Crew_Icon.png</t>
+        </is>
+      </c>
       <c r="V103"/>
       <c r="W103"/>
       <c r="X103"/>
@@ -8414,12 +8436,12 @@
       <c r="C104"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yutori_Natsu</t>
+          <t xml:space="preserve">Tsuchinaga_Hiyori</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">유토리 나츠</t>
+          <t xml:space="preserve">츠치나가 히요리</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8428,46 +8450,54 @@
         </is>
       </c>
       <c r="G104">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I104">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">After_School_Sweets_Club</t>
+          <t xml:space="preserve">Arius_Squad</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRONT</t>
+          <t xml:space="preserve">BACK</t>
         </is>
       </c>
       <c r="L104"/>
       <c r="M104"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBA_exhaust;EOT_move_gain_dessert</t>
+          <t xml:space="preserve">SOT_usemana1_PS_draw</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve">공격을 하지 않습니다. 자신의 턴 종료 시, 무작위 위치로 이동하며, 디저트 하나를 무작위로 패로 가져옵니다.</t>
+          <t xml:space="preserve">자신의 차례 시작 시, 마나를 하나 제거하고 카드를 한 장 뽑습니다.</t>
         </is>
       </c>
       <c r="P104"/>
       <c r="Q104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104">
         <v>100</v>
       </c>
       <c r="S104"/>
-      <c r="T104"/>
-      <c r="U104"/>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Tsuchinaga_Hiyori/Tsuchinaga_Hiyori_Card.png</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Arius/Arius_Squad/Tsuchinaga_Hiyori/Tsuchinaga_Hiyori_Board.png</t>
+        </is>
+      </c>
       <c r="V104"/>
       <c r="W104"/>
       <c r="X104"/>
@@ -8484,52 +8514,68 @@
       <c r="C105"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">arona_attack</t>
+          <t xml:space="preserve">Urawa_Hanako</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">지정 사격</t>
+          <t xml:space="preserve">우라와 하나코</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105"/>
+        <v>4</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Make_Up_Work_Club</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">MIDDLE</t>
         </is>
       </c>
       <c r="L105"/>
       <c r="M105"/>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">activate_damage2</t>
-        </is>
-      </c>
-      <c r="O105"/>
+          <t xml:space="preserve">OP_create_SH3</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등교 : '수상한 하니와' 3장을 패로 가져옵니다.</t>
+        </is>
+      </c>
       <c r="P105"/>
       <c r="Q105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105">
         <v>100</v>
       </c>
       <c r="S105"/>
-      <c r="T105"/>
-      <c r="U105"/>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Urawa_Hanako/Urawa_Hanako_Card.png</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Make_Up_Work_Club/Urawa_Hanako/Urawa_Hanako_Board.png</t>
+        </is>
+      </c>
       <c r="V105"/>
       <c r="W105"/>
       <c r="X105"/>
@@ -8546,44 +8592,48 @@
       <c r="C106"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">arona_move</t>
+          <t xml:space="preserve">Ushimaki_Juri</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">이동 명령</t>
+          <t xml:space="preserve">우시마키 주리</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero</t>
+          <t xml:space="preserve">Student</t>
         </is>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106"/>
+        <v>5</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School_Lunch_Club</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">NONE</t>
+          <t xml:space="preserve">FRONT</t>
         </is>
       </c>
       <c r="L106"/>
       <c r="M106"/>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">activate_move_ally</t>
+          <t xml:space="preserve">OBA_exhaust_damage</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve">지정한 아군 유닛을 주변 한 칸으로 이동시킵니다. (장소 카드는 제외)</t>
+          <t xml:space="preserve">공격하는 대신 사거리 내의 모든 유닛에게 자신의 공격력만큼 피해를 줍니다.</t>
         </is>
       </c>
       <c r="P106"/>
@@ -8594,16 +8644,8 @@
         <v>100</v>
       </c>
       <c r="S106"/>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Arona/Arona_Move/Arona_Move_Card.png</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Arona/Arona_Move/Arona_Move_Board.png</t>
-        </is>
-      </c>
+      <c r="T106"/>
+      <c r="U106"/>
       <c r="V106"/>
       <c r="W106"/>
       <c r="X106"/>
@@ -8620,6 +8662,442 @@
       <c r="C107"/>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Uzawa_Reisa</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우자와 레이사</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student</t>
+        </is>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
+        <v>4</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trinity_Vigilante_Crew</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L107"/>
+      <c r="M107"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP_move_enemy</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등교 : 상대 유닛을 지정합니다. 해당 유닛을 이 유닛의 사거리 내의 원하는 타일로 이동시킵니다,</t>
+        </is>
+      </c>
+      <c r="P107"/>
+      <c r="Q107">
+        <v>1</v>
+      </c>
+      <c r="R107">
+        <v>100</v>
+      </c>
+      <c r="S107"/>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Uzawa_Reisa/Uzawa_Reisa_Card.png</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Trinity/Trinity_Vigilante_Crew/Uzawa_Reisa/Uzawa_Reisa_Board.png</t>
+        </is>
+      </c>
+      <c r="V107"/>
+      <c r="W107"/>
+      <c r="X107"/>
+      <c r="Y107"/>
+      <c r="Z107"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sound/Voice/Trinity/Trinity_Vigilante_Crew/Reisa/Reisa_CommonSkill.mp3</t>
+        </is>
+      </c>
+      <c r="AB107"/>
+      <c r="AC107"/>
+      <c r="AD107"/>
+    </row>
+    <row r="108">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wanibuchi_Akari</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">와니부치 아카리</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student</t>
+        </is>
+      </c>
+      <c r="G108">
+        <v>3</v>
+      </c>
+      <c r="H108">
+        <v>3</v>
+      </c>
+      <c r="I108">
+        <v>10</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gourmet_Research_Society</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIDDLE</t>
+        </is>
+      </c>
+      <c r="L108"/>
+      <c r="M108"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP_damage_self_7</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등교 : 자기 자신에게 7 피해를 줍니다.</t>
+        </is>
+      </c>
+      <c r="P108"/>
+      <c r="Q108">
+        <v>1</v>
+      </c>
+      <c r="R108">
+        <v>100</v>
+      </c>
+      <c r="S108"/>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Wanibuchi_Akari/Wanibuchi_Akari-Card.png</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Student/Gehenna/Gourmet_Research_Society/Wanibuchi_Akari/Wanibuchi_Akari_Board.png</t>
+        </is>
+      </c>
+      <c r="V108"/>
+      <c r="W108"/>
+      <c r="X108"/>
+      <c r="Y108"/>
+      <c r="Z108"/>
+      <c r="AA108"/>
+      <c r="AB108"/>
+      <c r="AC108"/>
+      <c r="AD108"/>
+    </row>
+    <row r="109">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yurizono_Seia</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유리조노 세이아</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student</t>
+        </is>
+      </c>
+      <c r="G109">
+        <v>4</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tea_Party</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIDDLE</t>
+        </is>
+      </c>
+      <c r="L109"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tea_party_host=0</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOT_ScryTop_Create</t>
+        </is>
+      </c>
+      <c r="O109"/>
+      <c r="P109"/>
+      <c r="Q109">
+        <v>1</v>
+      </c>
+      <c r="R109">
+        <v>100</v>
+      </c>
+      <c r="S109"/>
+      <c r="T109"/>
+      <c r="U109"/>
+      <c r="V109"/>
+      <c r="W109"/>
+      <c r="X109"/>
+      <c r="Y109"/>
+      <c r="Z109"/>
+      <c r="AA109"/>
+      <c r="AB109"/>
+      <c r="AC109"/>
+      <c r="AD109"/>
+    </row>
+    <row r="110">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yutori_Natsu</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유토리 나츠</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Student</t>
+        </is>
+      </c>
+      <c r="G110">
+        <v>3</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>6</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After_School_Sweets_Club</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRONT</t>
+        </is>
+      </c>
+      <c r="L110"/>
+      <c r="M110"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBA_exhaust;EOT_move_gain_dessert</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공격을 하지 않습니다. 자신의 턴 종료 시, 무작위 위치로 이동하며, 디저트 하나를 무작위로 패로 가져옵니다.</t>
+        </is>
+      </c>
+      <c r="P110"/>
+      <c r="Q110">
+        <v>0</v>
+      </c>
+      <c r="R110">
+        <v>100</v>
+      </c>
+      <c r="S110"/>
+      <c r="T110"/>
+      <c r="U110"/>
+      <c r="V110"/>
+      <c r="W110"/>
+      <c r="X110"/>
+      <c r="Y110"/>
+      <c r="Z110"/>
+      <c r="AA110"/>
+      <c r="AB110"/>
+      <c r="AC110"/>
+      <c r="AD110"/>
+    </row>
+    <row r="111">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arona_attack</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지정 사격</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hero</t>
+        </is>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NONE</t>
+        </is>
+      </c>
+      <c r="L111"/>
+      <c r="M111"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activate_damage2</t>
+        </is>
+      </c>
+      <c r="O111"/>
+      <c r="P111"/>
+      <c r="Q111">
+        <v>0</v>
+      </c>
+      <c r="R111">
+        <v>100</v>
+      </c>
+      <c r="S111"/>
+      <c r="T111"/>
+      <c r="U111"/>
+      <c r="V111"/>
+      <c r="W111"/>
+      <c r="X111"/>
+      <c r="Y111"/>
+      <c r="Z111"/>
+      <c r="AA111"/>
+      <c r="AB111"/>
+      <c r="AC111"/>
+      <c r="AD111"/>
+    </row>
+    <row r="112">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arona_move</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이동 명령</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hero</t>
+        </is>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NONE</t>
+        </is>
+      </c>
+      <c r="L112"/>
+      <c r="M112"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">activate_move_ally</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지정한 아군 유닛을 주변 한 칸으로 이동시킵니다. (장소 카드는 제외)</t>
+        </is>
+      </c>
+      <c r="P112"/>
+      <c r="Q112">
+        <v>0</v>
+      </c>
+      <c r="R112">
+        <v>100</v>
+      </c>
+      <c r="S112"/>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Arona/Arona_Move/Arona_Move_Card.png</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/TcgEngine/Sprites/Cards/Arona/Arona_Move/Arona_Move_Board.png</t>
+        </is>
+      </c>
+      <c r="V112"/>
+      <c r="W112"/>
+      <c r="X112"/>
+      <c r="Y112"/>
+      <c r="Z112"/>
+      <c r="AA112"/>
+      <c r="AB112"/>
+      <c r="AC112"/>
+      <c r="AD112"/>
+    </row>
+    <row r="113">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113" t="inlineStr">
+        <is>
           <t xml:space="preserve">!EndTable</t>
         </is>
       </c>

--- a/CardArchive/Tools/DataExport/CardData.xlsx
+++ b/CardArchive/Tools/DataExport/CardData.xlsx
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">야전 정비 드론</t>
+          <t xml:space="preserve">전함 힐</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2526,14 +2526,10 @@
       <c r="J21"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">BACK</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MIDDLE</t>
+        </is>
+      </c>
+      <c r="L21"/>
       <c r="M21"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -2542,7 +2538,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">긴급 수리</t>
+          <t xml:space="preserve">기계 타입 유닛에게 공격력 1 부여</t>
         </is>
       </c>
       <c r="P21"/>
@@ -2643,7 +2639,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3066,7 +3062,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">중장갑 경비 로봇</t>
+          <t xml:space="preserve">중~고코 깡스탯</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3089,11 +3085,7 @@
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+      <c r="L29"/>
       <c r="M29"/>
       <c r="N29"/>
       <c r="O29"/>
@@ -4114,7 +4106,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve">미식연구부 동아리 효과가 피해 대신 파괴로 바뀐다.</t>
+          <t xml:space="preserve">미식연구부 동아리 효과가 피해 대신 파괴로 바꾼다.</t>
         </is>
       </c>
       <c r="P43"/>
@@ -4301,7 +4293,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -4867,11 +4859,7 @@
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+      <c r="L54"/>
       <c r="M54"/>
       <c r="N54" t="inlineStr">
         <is>
@@ -6111,7 +6099,7 @@
         </is>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -6181,13 +6169,13 @@
         </is>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J72"/>
       <c r="K72" t="inlineStr">
@@ -6340,7 +6328,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">선택한 열의 모든 유닛에게 4의 피해를 준다.</t>
+          <t xml:space="preserve">선택한 열의 모든 유닛에게 6의 피해를 준다.</t>
         </is>
       </c>
       <c r="P74"/>
@@ -6440,7 +6428,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">경비 로봇</t>
+          <t xml:space="preserve">저코 깡스탯</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6463,11 +6451,7 @@
           <t xml:space="preserve">FRONT</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">machine</t>
-        </is>
-      </c>
+      <c r="L76"/>
       <c r="M76"/>
       <c r="N76"/>
       <c r="O76"/>
@@ -7734,7 +7718,7 @@
         </is>
       </c>
       <c r="G94">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -7854,10 +7838,10 @@
         </is>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H96">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I96">
         <v>2</v>
@@ -7881,7 +7865,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve">속사</t>
+          <t xml:space="preserve">속사, 유닛보다 플레이어 우선</t>
         </is>
       </c>
       <c r="P96"/>
